--- a/Datas/Monster.xlsx
+++ b/Datas/Monster.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="36">
   <si>
     <t>##var</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t>Type</t>
+  </si>
+  <si>
+    <t>MoveType</t>
   </si>
   <si>
     <t>DropIds#sep=,</t>
@@ -100,6 +103,9 @@
     <t>怪物类型</t>
   </si>
   <si>
+    <t>怪物移动类型</t>
+  </si>
+  <si>
     <t>掉落物</t>
   </si>
   <si>
@@ -118,6 +124,9 @@
     <t>MonsterType</t>
   </si>
   <si>
+    <t>MonsterMoveType</t>
+  </si>
+  <si>
     <t>list,int</t>
   </si>
   <si>
@@ -130,6 +139,9 @@
     <t>MElEE</t>
   </si>
   <si>
+    <t>WALK</t>
+  </si>
+  <si>
     <t>1,2</t>
   </si>
   <si>
@@ -137,6 +149,9 @@
   </si>
   <si>
     <t>卡芮恩</t>
+  </si>
+  <si>
+    <t>FLY</t>
   </si>
 </sst>
 </file>
@@ -1289,10 +1304,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="6"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1323,82 +1338,91 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J3" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="K3" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:11">
       <c r="B5">
         <v>5001</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D5">
         <v>100</v>
@@ -1413,21 +1437,24 @@
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J5" t="s">
-        <v>28</v>
+        <v>32</v>
+      </c>
+      <c r="K5" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:11">
       <c r="B6">
         <v>5002</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D6">
         <v>50</v>
@@ -1442,21 +1469,24 @@
         <v>2</v>
       </c>
       <c r="H6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J6" t="s">
-        <v>28</v>
+        <v>32</v>
+      </c>
+      <c r="K6" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:11">
       <c r="B7">
         <v>5003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D7">
         <v>75</v>
@@ -1471,13 +1501,16 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I7" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="J7" t="s">
-        <v>28</v>
+        <v>32</v>
+      </c>
+      <c r="K7" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/Monster.xlsx
+++ b/Datas/Monster.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="41">
   <si>
     <t>##var</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t>Type</t>
+  </si>
+  <si>
+    <t>PrefabName</t>
   </si>
   <si>
     <t>MoveType</t>
@@ -103,6 +106,9 @@
     <t>怪物类型</t>
   </si>
   <si>
+    <t>预制体名字</t>
+  </si>
+  <si>
     <t>怪物移动类型</t>
   </si>
   <si>
@@ -139,6 +145,9 @@
     <t>MElEE</t>
   </si>
   <si>
+    <t>velom</t>
+  </si>
+  <si>
     <t>WALK</t>
   </si>
   <si>
@@ -148,7 +157,13 @@
     <t>伽洛斯</t>
   </si>
   <si>
+    <t>garos</t>
+  </si>
+  <si>
     <t>卡芮恩</t>
+  </si>
+  <si>
+    <t>karien</t>
   </si>
   <si>
     <t>FLY</t>
@@ -1304,10 +1319,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="6"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1341,88 +1356,97 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I3" t="s">
         <v>26</v>
       </c>
       <c r="J3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K3" t="s">
-        <v>27</v>
+        <v>29</v>
+      </c>
+      <c r="L3" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:12">
       <c r="B5">
         <v>5001</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D5">
         <v>100</v>
@@ -1437,24 +1461,27 @@
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K5" t="s">
-        <v>32</v>
+        <v>35</v>
+      </c>
+      <c r="L5" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:12">
       <c r="B6">
         <v>5002</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D6">
         <v>50</v>
@@ -1469,24 +1496,27 @@
         <v>2</v>
       </c>
       <c r="H6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I6" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="J6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K6" t="s">
-        <v>32</v>
+        <v>35</v>
+      </c>
+      <c r="L6" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:12">
       <c r="B7">
         <v>5003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D7">
         <v>75</v>
@@ -1501,16 +1531,19 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I7" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" t="s">
+        <v>40</v>
+      </c>
+      <c r="K7" t="s">
         <v>35</v>
       </c>
-      <c r="J7" t="s">
-        <v>32</v>
-      </c>
-      <c r="K7" t="s">
-        <v>32</v>
+      <c r="L7" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/Monster.xlsx
+++ b/Datas/Monster.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="46">
   <si>
     <t>##var</t>
   </si>
@@ -63,6 +63,12 @@
   </si>
   <si>
     <t>SkillIds#sep=,</t>
+  </si>
+  <si>
+    <t>AttackRange</t>
+  </si>
+  <si>
+    <t>AttackSpeed</t>
   </si>
   <si>
     <t>##</t>
@@ -118,6 +124,12 @@
     <t>技能</t>
   </si>
   <si>
+    <t>攻击范围</t>
+  </si>
+  <si>
+    <t>攻速</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -134,6 +146,9 @@
   </si>
   <si>
     <t>list,int</t>
+  </si>
+  <si>
+    <t>float</t>
   </si>
   <si>
     <t>##group</t>
@@ -1319,10 +1334,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="6"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1359,94 +1374,112 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="L3" t="s">
-        <v>29</v>
+        <v>33</v>
+      </c>
+      <c r="M3" t="s">
+        <v>34</v>
+      </c>
+      <c r="N3" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:14">
       <c r="B5">
         <v>5001</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D5">
         <v>100</v>
@@ -1458,30 +1491,36 @@
         <v>5</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H5" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I5" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="K5" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="L5" t="s">
-        <v>35</v>
+        <v>40</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:14">
       <c r="B6">
         <v>5002</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D6">
         <v>50</v>
@@ -1496,27 +1535,33 @@
         <v>2</v>
       </c>
       <c r="H6" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I6" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J6" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="K6" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="L6" t="s">
-        <v>35</v>
+        <v>40</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
+      </c>
+      <c r="N6">
+        <v>0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:14">
       <c r="B7">
         <v>5003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D7">
         <v>75</v>
@@ -1531,19 +1576,25 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I7" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K7" t="s">
         <v>40</v>
       </c>
-      <c r="K7" t="s">
-        <v>35</v>
-      </c>
       <c r="L7" t="s">
-        <v>35</v>
+        <v>40</v>
+      </c>
+      <c r="M7">
+        <v>8</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/Monster.xlsx
+++ b/Datas/Monster.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="49">
   <si>
     <t>##var</t>
   </si>
@@ -69,6 +69,9 @@
   </si>
   <si>
     <t>AttackSpeed</t>
+  </si>
+  <si>
+    <t>BulletId</t>
   </si>
   <si>
     <t>##</t>
@@ -130,6 +133,26 @@
     <t>攻速</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>子弹</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ID</t>
+    </r>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -170,6 +193,9 @@
   </si>
   <si>
     <t>伽洛斯</t>
+  </si>
+  <si>
+    <t>RANGED</t>
   </si>
   <si>
     <t>garos</t>
@@ -1334,10 +1360,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="6"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1380,106 +1406,115 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L3" t="s">
+        <v>35</v>
+      </c>
+      <c r="M3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N3" t="s">
+        <v>36</v>
+      </c>
+      <c r="O3" t="s">
         <v>31</v>
       </c>
-      <c r="I3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J3" t="s">
-        <v>32</v>
-      </c>
-      <c r="K3" t="s">
-        <v>33</v>
-      </c>
-      <c r="L3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M3" t="s">
-        <v>34</v>
-      </c>
-      <c r="N3" t="s">
-        <v>34</v>
-      </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:15">
       <c r="B5">
         <v>5001</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D5">
         <v>100</v>
@@ -1494,19 +1529,19 @@
         <v>3</v>
       </c>
       <c r="H5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -1515,12 +1550,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:15">
       <c r="B6">
         <v>5002</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D6">
         <v>50</v>
@@ -1535,19 +1570,19 @@
         <v>2</v>
       </c>
       <c r="H6" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K6" t="s">
         <v>42</v>
       </c>
-      <c r="J6" t="s">
-        <v>39</v>
-      </c>
-      <c r="K6" t="s">
-        <v>40</v>
-      </c>
       <c r="L6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M6">
         <v>6</v>
@@ -1555,13 +1590,16 @@
       <c r="N6">
         <v>0.5</v>
       </c>
+      <c r="O6">
+        <v>20001</v>
+      </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:15">
       <c r="B7">
         <v>5003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D7">
         <v>75</v>
@@ -1576,25 +1614,25 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M7">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
